--- a/output/xlsx/ExtracaoOffline--GT-.xlsx
+++ b/output/xlsx/ExtracaoOffline--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="72">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 9 test case(s)</t>
+    <t>Size: 8 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -155,6 +155,9 @@
     <t>operador: le (via leitor de codigo de barras) um product number e serial number validos</t>
   </si>
   <si>
+    <t>SYSTEM processes action successfully</t>
+  </si>
+  <si>
     <t>TC6</t>
   </si>
   <si>
@@ -170,61 +173,46 @@
     <t>TC7</t>
   </si>
   <si>
-    <t>Alternative Flow 6: Product number e serial number que nao casam</t>
-  </si>
-  <si>
-    <t>operador: digita um product number e serial number validos mas nao referentes a mesma familia e pressiona Extract (terminal em modo LLT)</t>
-  </si>
-  <si>
-    <t>SYSTEM apresenta mensagem de erro</t>
+    <t xml:space="preserve">Exception Flow 1: Sem conexao e usuario deseja entrar em modo offline </t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem solicitando confirmacao se usuario quer entrar em modo offline</t>
+  </si>
+  <si>
+    <t>operador: confirma que quer entrar em modo offline</t>
+  </si>
+  <si>
+    <t>operador: realiza uma serie de extracoes sequenciais</t>
+  </si>
+  <si>
+    <t>operador: reastabelece conexao</t>
+  </si>
+  <si>
+    <t>SYSTEM envia extracoes locais para o servidor e as apaga da pasta local 'OfflineExtraction'</t>
+  </si>
+  <si>
+    <t>operador: loga no servidor e vai ate a pagina de extracoes</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe lista com extracoes realizadas no modo offline</t>
+  </si>
+  <si>
+    <t>Flow interrupted due to exception / error</t>
   </si>
   <si>
     <t>TC8</t>
   </si>
   <si>
-    <t xml:space="preserve">Exception Flow 1: Sem conexao e usuario deseja entrar em modo offline </t>
-  </si>
-  <si>
-    <t>SYSTEM exibe mensagem solicitando confirmacao se usuario quer entrar em modo offline</t>
-  </si>
-  <si>
-    <t>operador: confirma que quer entrar em modo offline</t>
-  </si>
-  <si>
-    <t>operador: realiza uma serie de extracoes sequenciais</t>
-  </si>
-  <si>
-    <t>operador: reastabelece conexao</t>
-  </si>
-  <si>
-    <t>SYSTEM envia extracoes locais para o servidor e as apaga da pasta local 'OfflineExtraction'</t>
-  </si>
-  <si>
-    <t>operador: loga no servidor e vai ate a pagina de extracoes</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe lista com extracoes realizadas no modo offline</t>
-  </si>
-  <si>
-    <t>Flow interrupted due to exception / error</t>
+    <t xml:space="preserve">Exception Flow 2: Sem conexao e usuario nao deseja entrar em modo offline </t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem solicitando confirmação se usuario quer entrar em modo offline</t>
+  </si>
+  <si>
+    <t>operador: nao deseja entrar em modo offline</t>
   </si>
   <si>
     <t>TC9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception Flow 2: Sem conexao e usuario nao deseja entrar em modo offline </t>
-  </si>
-  <si>
-    <t>SYSTEM exibe mensagem solicitando confirmação se usuario quer entrar em modo offline</t>
-  </si>
-  <si>
-    <t>operador: nao deseja entrar em modo offline</t>
-  </si>
-  <si>
-    <t>SYSTEM processes action successfully</t>
-  </si>
-  <si>
-    <t>TC10</t>
   </si>
   <si>
     <t>Exception Flow 3: Cai conexao novamente</t>
@@ -331,11 +319,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="114.3671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="88.19921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="83.125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -808,7 +796,7 @@
         <v>27</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s" s="3">
         <v>27</v>
@@ -830,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s" s="1">
         <v>13</v>
@@ -844,7 +832,7 @@
         <v>15</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s" s="1">
         <v>17</v>
@@ -903,13 +891,13 @@
         <v>2.0</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D49" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s" s="3">
         <v>27</v>
@@ -951,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>13</v>
@@ -965,7 +953,7 @@
         <v>15</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s" s="1">
         <v>17</v>
@@ -1044,7 +1032,7 @@
         <v>3.0</v>
       </c>
       <c r="B60" t="s" s="3">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s" s="3">
         <v>27</v>
@@ -1064,13 +1052,13 @@
         <v>4.0</v>
       </c>
       <c r="B61" t="s" s="3">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C61" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>27</v>
@@ -1084,13 +1072,13 @@
         <v>5.0</v>
       </c>
       <c r="B62" t="s" s="3">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D62" t="s" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E62" t="s" s="3">
         <v>27</v>
@@ -1100,118 +1088,118 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s" s="1">
+      <c r="A63" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B63" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="C63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s" s="3">
+        <v>58</v>
+      </c>
+      <c r="E63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B64" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="C64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s" s="3">
+        <v>60</v>
+      </c>
+      <c r="E64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="B63" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C66" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="E67" t="s" s="1">
-        <v>17</v>
+      <c r="B65" t="s" s="0">
+        <v>61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="E69" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="B70" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B69" t="s" s="2">
+      <c r="B71" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C69" t="s" s="2">
+      <c r="C71" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D69" t="s" s="2">
+      <c r="D71" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E69" t="s" s="2">
+      <c r="E71" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F69" t="s" s="2">
+      <c r="F71" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B70" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C70" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D70" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E70" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F70" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B71" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D71" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n" s="4">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B72" t="s" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D72" t="s" s="3">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s" s="3">
         <v>27</v>
@@ -1222,16 +1210,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n" s="4">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="B73" t="s" s="3">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D73" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E73" t="s" s="3">
         <v>27</v>
@@ -1242,16 +1230,16 @@
     </row>
     <row r="74">
       <c r="A74" t="n" s="4">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="E74" t="s" s="3">
         <v>27</v>
@@ -1262,117 +1250,117 @@
     </row>
     <row r="75">
       <c r="A75" t="n" s="4">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="B75" t="s" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C75" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D75" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="E75" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F75" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B76" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E75" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F75" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B76" t="s" s="3">
-        <v>62</v>
-      </c>
-      <c r="C76" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D76" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E76" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F76" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B77" t="s" s="0">
-        <v>64</v>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C79" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="C80" t="s" s="1">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="E81" t="s" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>19</v>
+      <c r="A82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>25</v>
+      <c r="A83" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B83" t="s" s="3">
+        <v>68</v>
+      </c>
+      <c r="C83" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D83" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="E83" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F83" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B84" t="s" s="3">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C84" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D84" t="s" s="3">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E84" t="s" s="3">
         <v>27</v>
@@ -1383,16 +1371,16 @@
     </row>
     <row r="85">
       <c r="A85" t="n" s="4">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="B85" t="s" s="3">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C85" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D85" t="s" s="3">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="E85" t="s" s="3">
         <v>27</v>
@@ -1402,172 +1390,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B86" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D86" t="s" s="3">
-        <v>67</v>
-      </c>
-      <c r="E86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F86" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>68</v>
-      </c>
-      <c r="C87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D87" t="s" s="3">
-        <v>69</v>
-      </c>
-      <c r="E87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F87" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="1">
+      <c r="A86" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="B88" t="s" s="0">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="C91" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="E92" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B93" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B95" t="s" s="3">
-        <v>72</v>
-      </c>
-      <c r="C95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D95" t="s" s="3">
-        <v>73</v>
-      </c>
-      <c r="E95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F95" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B96" t="s" s="3">
-        <v>60</v>
-      </c>
-      <c r="C96" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D96" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="E96" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F96" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B97" t="s" s="3">
-        <v>62</v>
-      </c>
-      <c r="C97" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D97" t="s" s="3">
-        <v>75</v>
-      </c>
-      <c r="E97" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F97" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B98" t="s" s="0">
-        <v>64</v>
+      <c r="B86" t="s" s="0">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/output/xlsx/ExtracaoOffline--GT-.xlsx
+++ b/output/xlsx/ExtracaoOffline--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="76">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 8 test case(s)</t>
+    <t>Size: 9 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -173,6 +173,18 @@
     <t>TC7</t>
   </si>
   <si>
+    <t>Alternative Flow 6: Product number e serial number que nao casam</t>
+  </si>
+  <si>
+    <t>operador: digita um product number e serial number validos mas nao referentes a mesma familia e pressiona Extract (terminal em modo LLT)</t>
+  </si>
+  <si>
+    <t>SYSTEM apresenta mensagem de erro</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exception Flow 1: Sem conexao e usuario deseja entrar em modo offline </t>
   </si>
   <si>
@@ -200,7 +212,7 @@
     <t>Flow interrupted due to exception / error</t>
   </si>
   <si>
-    <t>TC8</t>
+    <t>TC9</t>
   </si>
   <si>
     <t xml:space="preserve">Exception Flow 2: Sem conexao e usuario nao deseja entrar em modo offline </t>
@@ -212,7 +224,7 @@
     <t>operador: nao deseja entrar em modo offline</t>
   </si>
   <si>
-    <t>TC9</t>
+    <t>TC10</t>
   </si>
   <si>
     <t>Exception Flow 3: Cai conexao novamente</t>
@@ -319,11 +331,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="88.19921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="114.3671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="83.125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -1032,13 +1044,13 @@
         <v>3.0</v>
       </c>
       <c r="B60" t="s" s="3">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D60" t="s" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E60" t="s" s="3">
         <v>27</v>
@@ -1052,13 +1064,13 @@
         <v>4.0</v>
       </c>
       <c r="B61" t="s" s="3">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>27</v>
@@ -1072,134 +1084,134 @@
         <v>5.0</v>
       </c>
       <c r="B62" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D62" t="s" s="3">
-        <v>39</v>
-      </c>
-      <c r="E62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B63" t="s" s="3">
+      <c r="C66" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C63" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D63" t="s" s="3">
-        <v>58</v>
-      </c>
-      <c r="E63" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F63" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B64" t="s" s="3">
-        <v>59</v>
-      </c>
-      <c r="C64" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D64" t="s" s="3">
-        <v>60</v>
-      </c>
-      <c r="E64" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>61</v>
+      <c r="E67" t="s" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="1">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="C68" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E68" t="s" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="E69" t="s" s="1">
-        <v>17</v>
+      <c r="A69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>19</v>
+      <c r="A70" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B70" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D70" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E70" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F70" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F71" t="s" s="2">
-        <v>25</v>
+      <c r="A71" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B71" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E71" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n" s="4">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="B72" t="s" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D72" t="s" s="3">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s" s="3">
         <v>27</v>
@@ -1210,16 +1222,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n" s="4">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="B73" t="s" s="3">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C73" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D73" t="s" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s" s="3">
         <v>27</v>
@@ -1230,16 +1242,16 @@
     </row>
     <row r="74">
       <c r="A74" t="n" s="4">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E74" t="s" s="3">
         <v>27</v>
@@ -1250,117 +1262,117 @@
     </row>
     <row r="75">
       <c r="A75" t="n" s="4">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="B75" t="s" s="3">
+        <v>61</v>
+      </c>
+      <c r="C75" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D75" t="s" s="3">
+        <v>62</v>
+      </c>
+      <c r="E75" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F75" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B76" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="C76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s" s="3">
+        <v>64</v>
+      </c>
+      <c r="E76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B77" t="s" s="0">
         <v>65</v>
-      </c>
-      <c r="C75" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D75" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="E75" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F75" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="C79" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E79" t="s" s="1">
-        <v>14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="C80" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E81" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B82" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
+    <row r="83">
+      <c r="A83" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B82" t="s" s="2">
+      <c r="B83" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C82" t="s" s="2">
+      <c r="C83" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D82" t="s" s="2">
+      <c r="D83" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E82" t="s" s="2">
+      <c r="E83" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F82" t="s" s="2">
+      <c r="F83" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B83" t="s" s="3">
-        <v>68</v>
-      </c>
-      <c r="C83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D83" t="s" s="3">
-        <v>69</v>
-      </c>
-      <c r="E83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F83" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B84" t="s" s="3">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C84" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D84" t="s" s="3">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="E84" t="s" s="3">
         <v>27</v>
@@ -1371,30 +1383,191 @@
     </row>
     <row r="85">
       <c r="A85" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B85" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C85" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E85" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F85" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B85" t="s" s="3">
-        <v>59</v>
-      </c>
-      <c r="C85" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D85" t="s" s="3">
+      <c r="B86" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s" s="3">
+        <v>68</v>
+      </c>
+      <c r="E86" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B87" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="C87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="E87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F87" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C91" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="E85" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F85" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="1">
+      <c r="E92" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B95" t="s" s="3">
+        <v>72</v>
+      </c>
+      <c r="C95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D95" t="s" s="3">
+        <v>73</v>
+      </c>
+      <c r="E95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F95" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B96" t="s" s="3">
+        <v>61</v>
+      </c>
+      <c r="C96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D96" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="E96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B97" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="C97" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D97" t="s" s="3">
+        <v>75</v>
+      </c>
+      <c r="E97" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F97" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="B86" t="s" s="0">
-        <v>61</v>
+      <c r="B98" t="s" s="0">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/output/xlsx/ExtracaoOffline--GT-.xlsx
+++ b/output/xlsx/ExtracaoOffline--GT-.xlsx
@@ -155,7 +155,7 @@
     <t>TC4</t>
   </si>
   <si>
-    <t xml:space="preserve">Exception Flow 2: Cai conexão e usuario nao quer entrar em modo offline </t>
+    <t xml:space="preserve">Exception Flow 2: Cai conexão e usuario quer entrar em modo offline </t>
   </si>
   <si>
     <t>administrador: não deseja entrar em modo offline</t>
@@ -257,7 +257,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.25" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.78125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="72.93359375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>

--- a/output/xlsx/ExtracaoOffline--GT-.xlsx
+++ b/output/xlsx/ExtracaoOffline--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="59">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 4 test case(s)</t>
+    <t>Size: 7 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuário está logado no servidor</t>
+    <t>Usuário não está logado no servidor</t>
   </si>
   <si>
     <t>#</t>
@@ -98,9 +98,33 @@
     <t/>
   </si>
   <si>
+    <t>SYSTEM exibe exibe mensagem perguntando se o usuário deseja entrar em modo offline</t>
+  </si>
+  <si>
+    <t>administrador: pressiona botão Yes</t>
+  </si>
+  <si>
     <t>SYSTEM exibe tela inicial 'SAFF extraction'</t>
   </si>
   <si>
+    <t>administrador: insere um 'Product number', 'Serial number', tipo de teste 'Pre_test' e pressiona 'Extract'</t>
+  </si>
+  <si>
+    <t>SYSTEM adiciona nova extração a pasta local'</t>
+  </si>
+  <si>
+    <t>administrador: loga no servidor</t>
+  </si>
+  <si>
+    <t>SYSTEM envia extrações da pasta local para o servidor e as deleta da máquina local</t>
+  </si>
+  <si>
+    <t>administrador: vai até a página de extrações</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe lista com a extração realizada no modo offline no topo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Postcondition: </t>
   </si>
   <si>
@@ -110,46 +134,58 @@
     <t>Alternative Flow 1: Pressiona NO</t>
   </si>
   <si>
-    <t>administrador: Não deseja entrar em modo offline</t>
+    <t>administrador: pressiona botão No</t>
+  </si>
+  <si>
+    <t>SYSTEM Fecha janela de mensagem</t>
   </si>
   <si>
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Offline sempre</t>
-  </si>
-  <si>
-    <t>administrador: define que o sistema sempre fará extrações offline</t>
-  </si>
-  <si>
-    <t>administrador: realiza cinco extrações</t>
-  </si>
-  <si>
-    <t>SYSTEM adiciona novas extrações a pasta local'</t>
+    <t>Alternative Flow 2: Test 1</t>
+  </si>
+  <si>
+    <t>administrador: insere um 'Product number', 'Serial number', tipo de teste 'Test 1' e pressiona 'Extract'</t>
   </si>
   <si>
     <t>TC4</t>
   </si>
   <si>
-    <t xml:space="preserve">Exception Flow 1: Cai conexão </t>
-  </si>
-  <si>
-    <t>SYSTEM processes action successfully</t>
-  </si>
-  <si>
-    <t>administrador: confirma que quer entrar em modo offline</t>
-  </si>
-  <si>
-    <t>administrador: reastabelece conexão</t>
-  </si>
-  <si>
-    <t>SYSTEM envia extrações locais para o servidor e as apaga da pasta local</t>
-  </si>
-  <si>
-    <t>administrador: loga no servidor e vai até a página de extrações</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe lista com extrações realizada no modo offline no topo</t>
+    <t>Alternative Flow 3: Test 2</t>
+  </si>
+  <si>
+    <t>administrador: insere um 'Product number', 'Serial number', tipo de teste 'Test 2' e pressiona 'Extract'</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>Alternative Flow 4: QA</t>
+  </si>
+  <si>
+    <t>administrador: insere um 'Product number', 'Serial number', tipo de teste 'QA' e pressiona 'Extract'</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>Alternative Flow 5: Product number ou serial number inválidos</t>
+  </si>
+  <si>
+    <t>administrador: insere um 'Product number' ou 'Serial number' inválidos e pressiona 'Extract'</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem solicitando informando que o product number ou serial number são inválidos</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>Exception Flow 2: Cai conexão com servidor</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem informando quantas extrações foram transferidas para o servidor com sucesso e deleta da pasta local as extrações enviadas com sucesso</t>
   </si>
   <si>
     <t>Flow interrupted due to exception / error</t>
@@ -244,13 +280,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.84765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="84.359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="58.00390625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="131.4765625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.578125" customWidth="true" bestFit="true"/>
   </cols>
@@ -368,159 +404,238 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B11" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="C11" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B12" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B13" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s" s="3">
         <v>27</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s" s="1">
-        <v>14</v>
+      <c r="A14" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B14" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="1">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B18" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F18" t="s" s="3">
-        <v>27</v>
+      <c r="A18" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E19" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B22" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B23" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s" s="3">
+        <v>41</v>
+      </c>
+      <c r="E23" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B24" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B25" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="E23" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>25</v>
+      <c r="C25" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F25" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n" s="4">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s" s="3">
         <v>27</v>
@@ -531,111 +646,111 @@
     </row>
     <row r="27">
       <c r="A27" t="n" s="4">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="B27" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E27" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B28" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s" s="3">
         <v>36</v>
       </c>
-      <c r="C27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s" s="3">
+      <c r="E28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="E27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E31" t="s" s="1">
-        <v>14</v>
+      <c r="B29" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B34" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B34" t="s" s="2">
+      <c r="B35" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C34" t="s" s="2">
+      <c r="C35" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D34" t="s" s="2">
+      <c r="D35" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E34" t="s" s="2">
+      <c r="E35" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F34" t="s" s="2">
+      <c r="F35" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B35" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C35" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D35" t="s" s="3">
-        <v>40</v>
-      </c>
-      <c r="E35" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F35" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B36" t="s" s="3">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s" s="3">
         <v>27</v>
@@ -652,16 +767,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n" s="4">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B37" t="s" s="3">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E37" t="s" s="3">
         <v>27</v>
@@ -672,16 +787,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n" s="4">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s" s="3">
         <v>27</v>
@@ -692,30 +807,694 @@
     </row>
     <row r="39">
       <c r="A39" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B39" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E39" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F39" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n" s="4">
         <v>5.0</v>
       </c>
-      <c r="B39" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="C39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D39" t="s" s="3">
+      <c r="B40" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F40" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="E39" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="1">
+      <c r="C44" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E45" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B48" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E48" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B49" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="B40" t="s" s="0">
-        <v>46</v>
+      <c r="C49" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E49" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F49" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B50" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C50" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F50" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B51" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E51" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F51" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B52" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E52" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F52" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E57" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B60" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D60" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F60" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B61" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C61" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D61" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E61" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B62" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="C62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B63" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B64" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B72" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F72" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B73" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E73" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F73" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B74" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="C74" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D74" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="E74" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F74" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B75" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D75" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E75" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F75" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B76" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B77" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E82" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B85" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E85" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F85" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B86" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D86" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E86" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F86" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B87" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F87" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B88" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="E88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
